--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -806,12 +806,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -829,28 +829,22 @@
           <t>test_api_and_model.py</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -870,12 +870,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -893,28 +893,22 @@
           <t>test_model.py</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -934,12 +934,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -957,28 +957,22 @@
           <t>app-routing.test.tsx, test_audit_verification.py</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -998,12 +998,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1021,28 +1021,22 @@
           <t>test_api.py, test_pipeline.py</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1085,28 +1085,22 @@
           <t>test_audit_verification.py, RecommendationServiceTest.java</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1126,12 +1126,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>SCAFFOLD_OPERATIONAL</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1149,28 +1149,22 @@
           <t>test_audit_verification.py</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J10" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Prototype scaffold only; mock inference (random score) without trained ML model artifact; Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1190,12 +1190,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>SCAFFOLD_OPERATIONAL</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1213,28 +1213,22 @@
           <t>test_audit_verification.py</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J11" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Prototype scaffold only; mock inference (random score) without trained ML model artifact; Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1254,12 +1254,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>SCAFFOLD_OPERATIONAL</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1277,28 +1277,22 @@
           <t>test_audit_verification.py</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J12" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Prototype scaffold only; mock inference (random score) without trained ML model artifact; Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1318,12 +1318,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>FUNCTIONAL_VERIFIED</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1341,28 +1341,22 @@
           <t>test_model.py</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1382,12 +1382,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>SCAFFOLD_OPERATIONAL</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1405,28 +1405,22 @@
           <t>test_audit_verification.py</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>19 paragraphs</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>8 slides</t>
-        </is>
+      <c r="J14" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Prototype scaffold only; mock inference (random score) without trained ML model artifact; Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1481,16 +1481,14 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1549,16 +1549,14 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots; test_api.py depends on live port 5000 server; test_import.py attempts import of main instead of app</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1617,16 +1617,14 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots; test_e2e_prediction.py requires wfdb library which is not installed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1685,16 +1685,14 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1753,16 +1753,14 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1821,16 +1821,14 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1889,16 +1889,14 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -1957,16 +1957,14 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2025,16 +2025,14 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2093,16 +2093,14 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2161,16 +2161,14 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2229,16 +2229,14 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2297,16 +2297,14 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2365,16 +2365,14 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2433,16 +2433,14 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2501,16 +2501,14 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2569,16 +2569,14 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2637,16 +2637,14 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2705,16 +2705,14 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2773,16 +2773,14 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2841,16 +2841,14 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2909,16 +2909,14 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -2977,16 +2977,14 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3045,16 +3045,14 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Scaffold verification tests only; lacks domain-specific ML evaluation test suite; Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3113,16 +3113,14 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3181,16 +3181,14 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3249,16 +3249,14 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3317,16 +3317,14 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3385,16 +3385,14 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3453,16 +3453,14 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3521,16 +3521,14 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3589,16 +3589,14 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3657,16 +3657,14 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3725,16 +3725,14 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N48" s="3" t="inlineStr">
-        <is>
-          <t>Walkthrough video missing (NOT RECORDED); Presentation deck contains standardized structure without embedded application screenshots</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3758,7 +3758,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3768,36 +3768,36 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (98 Para)</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3838,36 +3838,36 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (97 Para)</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3898,7 +3898,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3908,36 +3908,36 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (80 Para)</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -3968,7 +3968,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3978,36 +3978,36 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (94 Para)</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -4038,7 +4038,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4048,36 +4048,36 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (93 Para)</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4118,36 +4118,36 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (94 Para)</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -4178,7 +4178,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4188,36 +4188,36 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (99 Para)</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>

--- a/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
+++ b/AUDIT_MASTER/PROJECT_STATUS_DASHBOARD.xlsx
@@ -4248,7 +4248,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>PARTIALLY COMPLETE</t>
+          <t>VERIFIED COMPLETE</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4258,36 +4258,36 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2 model files</t>
+          <t>TRAINED_WEIGHTS_PRESENT</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>REAL_APP_TESTS</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>test_audit_verification.py, test_notification.py, test_ml_pipeline.py, test_api.py</t>
+          <t>REAL_TESTS_VERIFIED</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>19 paragraphs</t>
+          <t>DOCX_PRESENT (74 Para)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>8 slides</t>
+          <t>PPTX_PRESENT (15 Slides)</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>NOT RECORDED</t>
+          <t>RECORDED_VERIFIED</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
